--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>123621493</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>123621478</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123621493</v>
+        <v>123621478</v>
       </c>
       <c r="B6" t="n">
-        <v>57857</v>
+        <v>58032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1279,6 +1279,11 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>bryn</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123621478</v>
+        <v>123621493</v>
       </c>
       <c r="B7" t="n">
-        <v>58029</v>
+        <v>57860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,16 +1317,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1338,7 +1343,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1398,11 +1403,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>bryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>123621478</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58033</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>123621493</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123621478</v>
+        <v>123621493</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1279,11 +1279,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>bryn</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1301,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123621493</v>
+        <v>123621478</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>58033</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,16 +1312,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1343,7 +1338,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1403,6 +1398,11 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>bryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1177,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123621493</v>
+        <v>123621478</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>58033</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1279,6 +1279,11 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>bryn</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,10 +1301,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123621478</v>
+        <v>123621493</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,16 +1317,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1338,7 +1343,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1398,11 +1403,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>bryn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,120 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125111179</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hallaholm, 350 NNO, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558844</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6452980</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Börkén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Börkén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1423,7 +1423,7 @@
         <v>125111179</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 31109-2020 artfynd.xlsx
+++ b/artfynd/A 31109-2020 artfynd.xlsx
@@ -1423,12 +1423,7 @@
         <v>125111179</v>
       </c>
       <c r="B8" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
